--- a/artfynd/A 38203-2022 artfynd.xlsx
+++ b/artfynd/A 38203-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38203-2022 artfynd.xlsx
+++ b/artfynd/A 38203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4530983</v>
+        <v>101975987</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222223</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O om Nydalen nära motorväg E4, Srm</t>
+          <t>Gältsund, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620184.682536503</v>
+        <v>620107</v>
       </c>
       <c r="R2" t="n">
-        <v>6518589.604707119</v>
+        <v>6518786</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-06-15</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-06-15</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +779,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>obesprutat åkerhörn</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6143845</v>
+        <v>4530983</v>
       </c>
       <c r="B3" t="n">
-        <v>103363</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224199</v>
+        <v>222223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småsnärjmåra</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium spurium subsp. vaillantii</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(DC.) Gaudin</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620184.682536503</v>
+        <v>620185</v>
       </c>
       <c r="R3" t="n">
-        <v>6518589.604707119</v>
+        <v>6518590</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +862,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +893,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6143845</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106347</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224199</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småsnärjmåra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galium spurium subsp. vaillantii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(DC.) Gaudin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>O om Nydalen nära motorväg E4, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>620185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6518590</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>obesprutat åkerhörn</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38203-2022 artfynd.xlsx
+++ b/artfynd/A 38203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101975987</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4530983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6143845</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>